--- a/apps/homework-wordcloud/sample_input/19990101.xlsx
+++ b/apps/homework-wordcloud/sample_input/19990101.xlsx
@@ -2314,12 +2314,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>411194059</t>
+          <t>990094059</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>411194059@gms.ndhu.edu.tw</t>
+          <t>990094059@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>411185750</t>
+          <t>990085750</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>411185750@gms.ndhu.edu.tw</t>
+          <t>990085750@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>411123578</t>
+          <t>990023578</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>411123578@gms.ndhu.edu.tw</t>
+          <t>990023578@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>411137045</t>
+          <t>990037045</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>411137045@gms.ndhu.edu.tw</t>
+          <t>990037045@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>411123457</t>
+          <t>990023457</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>411123457@gms.ndhu.edu.tw</t>
+          <t>990023457@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>411153669</t>
+          <t>990053669</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>411153669@gms.ndhu.edu.tw</t>
+          <t>990053669@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>411112230</t>
+          <t>990012230</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>411112230@gms.ndhu.edu.tw</t>
+          <t>990012230@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>411162982</t>
+          <t>990062982</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>411162982@gms.ndhu.edu.tw</t>
+          <t>990062982@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>411148558</t>
+          <t>990048558</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>411148558@gms.ndhu.edu.tw</t>
+          <t>990048558@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2539,12 +2539,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>411127143</t>
+          <t>990027143</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>411127143@gms.ndhu.edu.tw</t>
+          <t>990027143@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>411183314</t>
+          <t>990083314</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>411183314@gms.ndhu.edu.tw</t>
+          <t>990083314@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>411168730</t>
+          <t>990068730</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>411168730@gms.ndhu.edu.tw</t>
+          <t>990068730@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>411130882</t>
+          <t>990030882</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>411130882@gms.ndhu.edu.tw</t>
+          <t>990030882@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>411115245</t>
+          <t>990015245</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>411115245@gms.ndhu.edu.tw</t>
+          <t>990015245@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>411118170</t>
+          <t>990018170</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>411118170@gms.ndhu.edu.tw</t>
+          <t>990018170@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>411124949</t>
+          <t>990024949</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>411124949@gms.ndhu.edu.tw</t>
+          <t>990024949@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>411130142</t>
+          <t>990030142</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>411130142@gms.ndhu.edu.tw</t>
+          <t>990030142@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>411135584</t>
+          <t>990035584</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>411135584@gms.ndhu.edu.tw</t>
+          <t>990035584@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>411142934</t>
+          <t>990042934</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>411142934@gms.ndhu.edu.tw</t>
+          <t>990042934@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>411195101</t>
+          <t>990095101</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>411195101@gms.ndhu.edu.tw</t>
+          <t>990095101@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>411111664</t>
+          <t>990011664</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>411111664@gms.ndhu.edu.tw</t>
+          <t>990011664@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>411146562</t>
+          <t>990046562</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>411146562@gms.ndhu.edu.tw</t>
+          <t>990046562@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E23" t="n">

--- a/apps/homework-wordcloud/sample_input/19990101.xlsx
+++ b/apps/homework-wordcloud/sample_input/19990101.xlsx
@@ -995,7 +995,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>想試試看用水當溶劑做簡單的實驗，減少有機溶劑的使用。</t>
+          <t>想試試看用水當溶劑做簡單的實驗，減少有機溶劑的使用。步驟要怎麼做？</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>我想在系上的活動推廣自備容器，減少廢棄物產生。</t>
+          <t>我想在系上的活動推廣自備容器，減少廢棄物產生。這對環境的影響有多大？</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>再生原料這一項，花蓮有很多農業剩餘資源，其實很適合做這種嘗試。</t>
+          <t>再生原料這一項，花蓮有很多農業剩餘資源，其實很適合做這種嘗試。如果改用替代原料會不會比較好？</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>使用比較安全的溶劑，離子液體和超臨界二氧化碳都是課本提到的替代選項。</t>
+          <t>使用比較安全的溶劑，離子液體和超臨界二氧化碳都是課本提到的替代選項。未來產業有可能全面改用嗎？</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>再生原料這一項，花蓮有很多農業剩餘資源，其實很適合做這種嘗試。</t>
+          <t>再生原料這一項，花蓮有很多農業剩餘資源，其實很適合做這種嘗試。如果改用替代原料會不會比較好？</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>使用比較安全的溶劑，離子液體和超臨界二氧化碳都是課本提到的替代選項。</t>
+          <t>使用比較安全的溶劑，離子液體和超臨界二氧化碳都是課本提到的替代選項。未來產業有可能全面改用嗎？</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>想試試看用水當溶劑做簡單的實驗，減少有機溶劑的使用。</t>
+          <t>想試試看用水當溶劑做簡單的實驗，減少有機溶劑的使用。步驟要怎麼做？</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>我想在系上的活動推廣自備容器，減少廢棄物產生。</t>
+          <t>我想在系上的活動推廣自備容器，減少廢棄物產生。這對環境的影響有多大？</t>
         </is>
       </c>
     </row>
